--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A39041B-5AE8-4817-B8BD-CB93DE6E5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4212E7E5-E2AB-471D-8911-1D8EB9650C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20445" yWindow="-12135" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HORAS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="360">
   <si>
     <t>Descripción</t>
   </si>
@@ -1105,6 +1105,18 @@
   </si>
   <si>
     <t>Rediseño de la pantalla de taller para optimizar el espacio y que todo sea más compacto y mejor, asi como la reunion para llegar a esos acuerdos</t>
+  </si>
+  <si>
+    <t>Se realiza ajuste para poder manejar las rápidas, tambien se modifica el ticket</t>
+  </si>
+  <si>
+    <t>Reunion para ver el tema de taller, fueron dos reuniones</t>
+  </si>
+  <si>
+    <t>Reunion para ver consultas y dudas sobre los inventarios físicos</t>
+  </si>
+  <si>
+    <t>Reunion para ver el comportamiento del almacen de oro y vendedor</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1421,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1561,6 +1573,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1941,7 +1956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K389"/>
+  <dimension ref="A1:K392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8458,7 +8473,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="5"/>
       <c r="C337" s="9">
         <v>46090</v>
@@ -8476,7 +8491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A338" s="5"/>
       <c r="C338" s="9">
         <v>46103</v>
@@ -8494,7 +8509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="5"/>
       <c r="C339" s="9">
         <v>46103</v>
@@ -8512,7 +8527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="5"/>
       <c r="C340" s="9">
         <v>46103</v>
@@ -8530,7 +8545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="5"/>
       <c r="C341" s="9">
         <v>46103</v>
@@ -8548,7 +8563,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A342" s="5"/>
       <c r="C342" s="9">
         <v>46103</v>
@@ -8566,7 +8581,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="5"/>
       <c r="C343" s="9">
         <v>46118</v>
@@ -8584,7 +8599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A344" s="5"/>
       <c r="C344" s="9">
         <v>46150</v>
@@ -8602,7 +8617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A345" s="5"/>
       <c r="C345" s="9">
         <v>46150</v>
@@ -8620,9 +8635,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A346" s="5"/>
-      <c r="C346" s="61">
+      <c r="C346" s="9">
         <v>46194</v>
       </c>
       <c r="D346" s="13" t="s">
@@ -8634,243 +8649,272 @@
       <c r="F346" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="H346" s="14">
+      <c r="H346" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="5"/>
-      <c r="C347" s="61"/>
-      <c r="D347" s="13"/>
-      <c r="E347" s="2"/>
-      <c r="F347" s="2"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C347" s="9">
+        <v>46200</v>
+      </c>
+      <c r="D347" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E347" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F347" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="H347" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="5"/>
-      <c r="C348" s="61"/>
-      <c r="D348" s="13"/>
+      <c r="C348" s="61">
+        <v>46213</v>
+      </c>
+      <c r="D348" s="13" t="s">
+        <v>357</v>
+      </c>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H348" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="5"/>
+      <c r="C349" s="61">
+        <v>46231</v>
+      </c>
+      <c r="D349" s="13" t="s">
+        <v>358</v>
+      </c>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A350" s="83" t="s">
+      <c r="H349" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="5"/>
+      <c r="C350" s="61">
+        <v>46232</v>
+      </c>
+      <c r="D350" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E350" s="2"/>
+      <c r="F350" s="2"/>
+      <c r="H350" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="5"/>
+      <c r="C351" s="61"/>
+      <c r="D351" s="13"/>
+      <c r="E351" s="2"/>
+      <c r="F351" s="2"/>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="5"/>
+      <c r="E352" s="2"/>
+      <c r="F352" s="2"/>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A353" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B350" s="83"/>
-      <c r="C350" s="83"/>
-      <c r="D350" s="83"/>
-      <c r="E350" s="83"/>
-      <c r="F350" s="83"/>
-      <c r="G350" s="16">
-        <f>SUM(G2:G349)</f>
+      <c r="B353" s="84"/>
+      <c r="C353" s="84"/>
+      <c r="D353" s="84"/>
+      <c r="E353" s="84"/>
+      <c r="F353" s="84"/>
+      <c r="G353" s="16">
+        <f>SUM(G2:G352)</f>
         <v>314.78999999999996</v>
       </c>
-      <c r="H350" s="16">
-        <f>SUM(H2:H349)</f>
-        <v>208.3</v>
-      </c>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A351" s="83" t="s">
+      <c r="H353" s="16">
+        <f>SUM(H2:H352)</f>
+        <v>214.3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A354" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="B351" s="83"/>
-      <c r="C351" s="83"/>
-      <c r="D351" s="83"/>
-      <c r="E351" s="83"/>
-      <c r="F351" s="83"/>
-      <c r="G351" s="16">
+      <c r="B354" s="84"/>
+      <c r="C354" s="84"/>
+      <c r="D354" s="84"/>
+      <c r="E354" s="84"/>
+      <c r="F354" s="84"/>
+      <c r="G354" s="16">
         <v>200</v>
       </c>
-      <c r="H351" s="16">
+      <c r="H354" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A352" s="83" t="s">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A355" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B352" s="83"/>
-      <c r="C352" s="83"/>
-      <c r="D352" s="83"/>
-      <c r="E352" s="83"/>
-      <c r="F352" s="83"/>
-      <c r="G352" s="17">
-        <f>G351*G350</f>
+      <c r="B355" s="84"/>
+      <c r="C355" s="84"/>
+      <c r="D355" s="84"/>
+      <c r="E355" s="84"/>
+      <c r="F355" s="84"/>
+      <c r="G355" s="17">
+        <f>G354*G353</f>
         <v>62957.999999999993</v>
       </c>
-      <c r="H352" s="18">
-        <f>H351*H350</f>
-        <v>62490</v>
-      </c>
-      <c r="J352">
+      <c r="H355" s="18">
+        <f>H354*H353</f>
+        <v>64290</v>
+      </c>
+      <c r="J355">
         <v>-500</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A353" s="83" t="s">
+    <row r="356" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A356" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="B353" s="83"/>
-      <c r="C353" s="83"/>
-      <c r="D353" s="83"/>
-      <c r="E353" s="83"/>
-      <c r="F353" s="83"/>
-      <c r="G353" s="72">
-        <f>G352+H352</f>
-        <v>125448</v>
-      </c>
-      <c r="H353" s="72"/>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A354" s="10"/>
-      <c r="B354" s="75" t="s">
+      <c r="B356" s="84"/>
+      <c r="C356" s="84"/>
+      <c r="D356" s="84"/>
+      <c r="E356" s="84"/>
+      <c r="F356" s="84"/>
+      <c r="G356" s="73">
+        <f>G355+H355</f>
+        <v>127248</v>
+      </c>
+      <c r="H356" s="73"/>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A357" s="10"/>
+      <c r="B357" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="C354" s="75"/>
-      <c r="D354" s="75"/>
-      <c r="E354" s="75"/>
-      <c r="F354" s="75"/>
-      <c r="G354" s="21"/>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A355" s="11">
+      <c r="C357" s="76"/>
+      <c r="D357" s="76"/>
+      <c r="E357" s="76"/>
+      <c r="F357" s="76"/>
+      <c r="G357" s="21"/>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A358" s="11">
         <v>45109</v>
       </c>
-      <c r="B355" s="76" t="s">
+      <c r="B358" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="C355" s="76"/>
-      <c r="D355" s="76"/>
-      <c r="E355" s="76"/>
-      <c r="F355" s="76"/>
-      <c r="G355" s="78">
-        <v>10000</v>
-      </c>
-      <c r="H355" s="78"/>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356" s="11"/>
-      <c r="B356" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="C356" s="79"/>
-      <c r="D356" s="79"/>
-      <c r="E356" s="79"/>
-      <c r="F356" s="79"/>
-      <c r="G356" s="78">
-        <v>5000</v>
-      </c>
-      <c r="H356" s="78"/>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A357" s="11">
-        <v>45278</v>
-      </c>
-      <c r="B357" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C357" s="77"/>
-      <c r="D357" s="77"/>
-      <c r="E357" s="77"/>
-      <c r="F357" s="77"/>
-      <c r="G357" s="78">
-        <v>9800</v>
-      </c>
-      <c r="H357" s="78"/>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A358" s="11"/>
-      <c r="B358" s="77"/>
       <c r="C358" s="77"/>
       <c r="D358" s="77"/>
       <c r="E358" s="77"/>
       <c r="F358" s="77"/>
-      <c r="G358" s="78">
+      <c r="G358" s="79">
+        <v>10000</v>
+      </c>
+      <c r="H358" s="79"/>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A359" s="11"/>
+      <c r="B359" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C359" s="80"/>
+      <c r="D359" s="80"/>
+      <c r="E359" s="80"/>
+      <c r="F359" s="80"/>
+      <c r="G359" s="79">
+        <v>5000</v>
+      </c>
+      <c r="H359" s="79"/>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A360" s="11">
+        <v>45278</v>
+      </c>
+      <c r="B360" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C360" s="78"/>
+      <c r="D360" s="78"/>
+      <c r="E360" s="78"/>
+      <c r="F360" s="78"/>
+      <c r="G360" s="79">
+        <v>9800</v>
+      </c>
+      <c r="H360" s="79"/>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A361" s="11"/>
+      <c r="B361" s="78"/>
+      <c r="C361" s="78"/>
+      <c r="D361" s="78"/>
+      <c r="E361" s="78"/>
+      <c r="F361" s="78"/>
+      <c r="G361" s="79">
         <v>78298</v>
       </c>
-      <c r="H358" s="78"/>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A359" s="11"/>
-      <c r="B359" s="77"/>
-      <c r="C359" s="77"/>
-      <c r="D359" s="77"/>
-      <c r="E359" s="77"/>
-      <c r="F359" s="77"/>
-      <c r="G359" s="78"/>
-      <c r="H359" s="78"/>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A360" s="11"/>
-      <c r="B360" s="77"/>
-      <c r="C360" s="77"/>
-      <c r="D360" s="77"/>
-      <c r="E360" s="77"/>
-      <c r="F360" s="77"/>
-      <c r="G360" s="78"/>
-      <c r="H360" s="78"/>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A361" s="11"/>
-      <c r="B361" s="77" t="s">
+      <c r="H361" s="79"/>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A362" s="11"/>
+      <c r="B362" s="78"/>
+      <c r="C362" s="78"/>
+      <c r="D362" s="78"/>
+      <c r="E362" s="78"/>
+      <c r="F362" s="78"/>
+      <c r="G362" s="79"/>
+      <c r="H362" s="79"/>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A363" s="11"/>
+      <c r="B363" s="78"/>
+      <c r="C363" s="78"/>
+      <c r="D363" s="78"/>
+      <c r="E363" s="78"/>
+      <c r="F363" s="78"/>
+      <c r="G363" s="79"/>
+      <c r="H363" s="79"/>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A364" s="11"/>
+      <c r="B364" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="C361" s="77"/>
-      <c r="D361" s="77"/>
-      <c r="E361" s="77"/>
-      <c r="F361" s="77"/>
-      <c r="G361" s="78">
-        <f>SUM(G355:H360)</f>
+      <c r="C364" s="78"/>
+      <c r="D364" s="78"/>
+      <c r="E364" s="78"/>
+      <c r="F364" s="78"/>
+      <c r="G364" s="79">
+        <f>SUM(G358:H363)</f>
         <v>103098</v>
       </c>
-      <c r="H361" s="78"/>
-    </row>
-    <row r="362" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A362" s="73" t="s">
+      <c r="H364" s="79"/>
+    </row>
+    <row r="365" spans="1:10" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A365" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="B362" s="73"/>
-      <c r="C362" s="73"/>
-      <c r="D362" s="73"/>
-      <c r="E362" s="73"/>
-      <c r="F362" s="73"/>
-      <c r="G362" s="74">
-        <f>G353-G361</f>
-        <v>22350</v>
-      </c>
-      <c r="H362" s="74"/>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A363" s="11"/>
-      <c r="B363" s="12"/>
-      <c r="C363" s="12"/>
-      <c r="D363" s="12"/>
-      <c r="E363" s="12"/>
-      <c r="F363" s="12"/>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A364" s="11"/>
-      <c r="B364" s="12"/>
-      <c r="C364" s="12"/>
-      <c r="D364" s="12"/>
-      <c r="E364" s="12"/>
-      <c r="F364" s="12"/>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A365" s="11"/>
-      <c r="B365" s="12"/>
-      <c r="C365" s="12"/>
-      <c r="D365" s="12"/>
-      <c r="E365" s="12"/>
-      <c r="F365" s="12"/>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B365" s="74"/>
+      <c r="C365" s="74"/>
+      <c r="D365" s="74"/>
+      <c r="E365" s="74"/>
+      <c r="F365" s="74"/>
+      <c r="G365" s="75">
+        <f>G356-G364</f>
+        <v>24150</v>
+      </c>
+      <c r="H365" s="75"/>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="11"/>
       <c r="B366" s="12"/>
       <c r="C366" s="12"/>
@@ -8878,7 +8922,7 @@
       <c r="E366" s="12"/>
       <c r="F366" s="12"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" s="11"/>
       <c r="B367" s="12"/>
       <c r="C367" s="12"/>
@@ -8886,7 +8930,7 @@
       <c r="E367" s="12"/>
       <c r="F367" s="12"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="11"/>
       <c r="B368" s="12"/>
       <c r="C368" s="12"/>
@@ -8991,121 +9035,103 @@
       <c r="F380" s="12"/>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A381" s="9"/>
-      <c r="B381" s="84" t="s">
+      <c r="A381" s="11"/>
+      <c r="B381" s="12"/>
+      <c r="C381" s="12"/>
+      <c r="D381" s="12"/>
+      <c r="E381" s="12"/>
+      <c r="F381" s="12"/>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A382" s="11"/>
+      <c r="B382" s="12"/>
+      <c r="C382" s="12"/>
+      <c r="D382" s="12"/>
+      <c r="E382" s="12"/>
+      <c r="F382" s="12"/>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A383" s="11"/>
+      <c r="B383" s="12"/>
+      <c r="C383" s="12"/>
+      <c r="D383" s="12"/>
+      <c r="E383" s="12"/>
+      <c r="F383" s="12"/>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A384" s="9"/>
+      <c r="B384" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="C381" s="84"/>
-      <c r="D381" s="84"/>
-      <c r="E381" s="84"/>
-      <c r="F381" s="84"/>
-      <c r="G381" s="20"/>
-      <c r="H381" s="20"/>
-      <c r="I381" s="7">
-        <f>G350+H350</f>
-        <v>523.08999999999992</v>
-      </c>
-      <c r="J381" s="7">
-        <f>I381</f>
-        <v>523.08999999999992</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A382" s="5"/>
-      <c r="B382" s="85" t="s">
+      <c r="C384" s="85"/>
+      <c r="D384" s="85"/>
+      <c r="E384" s="85"/>
+      <c r="F384" s="85"/>
+      <c r="G384" s="20"/>
+      <c r="H384" s="20"/>
+      <c r="I384" s="7">
+        <f>G353+H353</f>
+        <v>529.08999999999992</v>
+      </c>
+      <c r="J384" s="7">
+        <f>I384</f>
+        <v>529.08999999999992</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A385" s="5"/>
+      <c r="B385" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="C382" s="85"/>
-      <c r="D382" s="85"/>
-      <c r="E382" s="85"/>
-      <c r="F382" s="85"/>
-      <c r="I382" s="7">
+      <c r="C385" s="86"/>
+      <c r="D385" s="86"/>
+      <c r="E385" s="86"/>
+      <c r="F385" s="86"/>
+      <c r="I385" s="7">
         <v>300</v>
       </c>
-      <c r="J382" s="7">
+      <c r="J385" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A383" s="5"/>
-      <c r="B383" s="85" t="s">
+    <row r="386" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A386" s="5"/>
+      <c r="B386" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="C383" s="85"/>
-      <c r="D383" s="85"/>
-      <c r="E383" s="85"/>
-      <c r="F383" s="85"/>
-      <c r="I383" s="8">
-        <f>I382*I381</f>
-        <v>156926.99999999997</v>
-      </c>
-      <c r="J383" s="8">
-        <f>J382*J381</f>
-        <v>104617.99999999999</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A384" s="22"/>
-      <c r="B384" s="86" t="s">
+      <c r="C386" s="86"/>
+      <c r="D386" s="86"/>
+      <c r="E386" s="86"/>
+      <c r="F386" s="86"/>
+      <c r="I386" s="8">
+        <f>I385*I384</f>
+        <v>158726.99999999997</v>
+      </c>
+      <c r="J386" s="8">
+        <f>J385*J384</f>
+        <v>105817.99999999999</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A387" s="22"/>
+      <c r="B387" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="C384" s="86"/>
-      <c r="D384" s="86"/>
-      <c r="E384" s="86"/>
-      <c r="F384" s="86"/>
-      <c r="G384" s="23"/>
-      <c r="H384" s="23"/>
-      <c r="I384" s="24"/>
-      <c r="J384" s="24"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A385" s="25">
+      <c r="C387" s="87"/>
+      <c r="D387" s="87"/>
+      <c r="E387" s="87"/>
+      <c r="F387" s="87"/>
+      <c r="G387" s="23"/>
+      <c r="H387" s="23"/>
+      <c r="I387" s="24"/>
+      <c r="J387" s="24"/>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A388" s="25">
         <v>45109</v>
       </c>
-      <c r="B385" s="81" t="s">
+      <c r="B388" s="82" t="s">
         <v>59</v>
-      </c>
-      <c r="C385" s="81"/>
-      <c r="D385" s="81"/>
-      <c r="E385" s="81"/>
-      <c r="F385" s="81"/>
-      <c r="G385" s="26"/>
-      <c r="H385" s="26"/>
-      <c r="I385" s="27">
-        <v>10000</v>
-      </c>
-      <c r="J385" s="27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A386" s="25"/>
-      <c r="B386" s="28"/>
-      <c r="C386" s="28"/>
-      <c r="D386" s="28"/>
-      <c r="E386" s="28"/>
-      <c r="F386" s="28"/>
-      <c r="G386" s="26"/>
-      <c r="H386" s="26"/>
-      <c r="I386" s="29"/>
-      <c r="J386" s="29"/>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A387" s="25"/>
-      <c r="B387" s="28"/>
-      <c r="C387" s="28"/>
-      <c r="D387" s="28"/>
-      <c r="E387" s="28"/>
-      <c r="F387" s="28"/>
-      <c r="G387" s="26"/>
-      <c r="H387" s="26"/>
-      <c r="I387" s="29"/>
-      <c r="J387" s="29"/>
-    </row>
-    <row r="388" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A388" s="25"/>
-      <c r="B388" s="82" t="s">
-        <v>62</v>
       </c>
       <c r="C388" s="82"/>
       <c r="D388" s="82"/>
@@ -9113,68 +9139,110 @@
       <c r="F388" s="82"/>
       <c r="G388" s="26"/>
       <c r="H388" s="26"/>
-      <c r="I388" s="30">
-        <f>SUM(I385:I387)</f>
+      <c r="I388" s="27">
         <v>10000</v>
       </c>
-      <c r="J388" s="30">
-        <f>SUM(J385:J387)</f>
+      <c r="J388" s="27">
         <v>10000</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A389" s="31">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A389" s="25"/>
+      <c r="B389" s="28"/>
+      <c r="C389" s="28"/>
+      <c r="D389" s="28"/>
+      <c r="E389" s="28"/>
+      <c r="F389" s="28"/>
+      <c r="G389" s="26"/>
+      <c r="H389" s="26"/>
+      <c r="I389" s="29"/>
+      <c r="J389" s="29"/>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A390" s="25"/>
+      <c r="B390" s="28"/>
+      <c r="C390" s="28"/>
+      <c r="D390" s="28"/>
+      <c r="E390" s="28"/>
+      <c r="F390" s="28"/>
+      <c r="G390" s="26"/>
+      <c r="H390" s="26"/>
+      <c r="I390" s="29"/>
+      <c r="J390" s="29"/>
+    </row>
+    <row r="391" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A391" s="25"/>
+      <c r="B391" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="C391" s="83"/>
+      <c r="D391" s="83"/>
+      <c r="E391" s="83"/>
+      <c r="F391" s="83"/>
+      <c r="G391" s="26"/>
+      <c r="H391" s="26"/>
+      <c r="I391" s="30">
+        <f>SUM(I388:I390)</f>
+        <v>10000</v>
+      </c>
+      <c r="J391" s="30">
+        <f>SUM(J388:J390)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A392" s="31">
         <v>45109</v>
       </c>
-      <c r="B389" s="80" t="s">
+      <c r="B392" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="C389" s="80"/>
-      <c r="D389" s="80"/>
-      <c r="E389" s="80"/>
-      <c r="F389" s="80"/>
-      <c r="G389" s="32"/>
-      <c r="H389" s="32"/>
-      <c r="I389" s="33">
-        <f>I383-I388</f>
-        <v>146926.99999999997</v>
-      </c>
-      <c r="J389" s="33">
-        <f>J383-J388</f>
-        <v>94617.999999999985</v>
+      <c r="C392" s="81"/>
+      <c r="D392" s="81"/>
+      <c r="E392" s="81"/>
+      <c r="F392" s="81"/>
+      <c r="G392" s="32"/>
+      <c r="H392" s="32"/>
+      <c r="I392" s="33">
+        <f>I386-I391</f>
+        <v>148726.99999999997</v>
+      </c>
+      <c r="J392" s="33">
+        <f>J386-J391</f>
+        <v>95817.999999999985</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B392:F392"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="A354:F354"/>
+    <mergeCell ref="A353:F353"/>
+    <mergeCell ref="A355:F355"/>
+    <mergeCell ref="A356:F356"/>
+    <mergeCell ref="B362:F362"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="B384:F384"/>
     <mergeCell ref="B385:F385"/>
-    <mergeCell ref="B388:F388"/>
-    <mergeCell ref="A351:F351"/>
-    <mergeCell ref="A350:F350"/>
-    <mergeCell ref="A352:F352"/>
-    <mergeCell ref="A353:F353"/>
-    <mergeCell ref="B359:F359"/>
-    <mergeCell ref="B360:F360"/>
-    <mergeCell ref="B381:F381"/>
-    <mergeCell ref="B382:F382"/>
-    <mergeCell ref="B383:F383"/>
-    <mergeCell ref="B384:F384"/>
-    <mergeCell ref="G353:H353"/>
-    <mergeCell ref="A362:F362"/>
-    <mergeCell ref="G362:H362"/>
-    <mergeCell ref="B354:F354"/>
-    <mergeCell ref="B355:F355"/>
-    <mergeCell ref="B361:F361"/>
-    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="B386:F386"/>
+    <mergeCell ref="B387:F387"/>
     <mergeCell ref="G356:H356"/>
-    <mergeCell ref="G361:H361"/>
+    <mergeCell ref="A365:F365"/>
+    <mergeCell ref="G365:H365"/>
+    <mergeCell ref="B357:F357"/>
+    <mergeCell ref="B358:F358"/>
+    <mergeCell ref="B364:F364"/>
     <mergeCell ref="G358:H358"/>
     <mergeCell ref="G359:H359"/>
+    <mergeCell ref="G364:H364"/>
+    <mergeCell ref="G361:H361"/>
+    <mergeCell ref="G362:H362"/>
+    <mergeCell ref="G363:H363"/>
     <mergeCell ref="G360:H360"/>
-    <mergeCell ref="G357:H357"/>
-    <mergeCell ref="B357:F357"/>
-    <mergeCell ref="B356:F356"/>
-    <mergeCell ref="B358:F358"/>
+    <mergeCell ref="B360:F360"/>
+    <mergeCell ref="B359:F359"/>
+    <mergeCell ref="B361:F361"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -9377,7 +9445,7 @@
       <c r="B19" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="89">
+      <c r="C19" s="90">
         <v>1100</v>
       </c>
       <c r="D19" s="38"/>
@@ -9387,7 +9455,7 @@
       <c r="B20" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="C20" s="90"/>
+      <c r="C20" s="91"/>
       <c r="D20" s="38"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9395,7 +9463,7 @@
       <c r="B21" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C21" s="91"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="38"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9403,7 +9471,7 @@
       <c r="B22" s="56" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="89">
+      <c r="C22" s="90">
         <v>600</v>
       </c>
       <c r="D22" s="38"/>
@@ -9413,7 +9481,7 @@
       <c r="B23" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="C23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="38"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9421,7 +9489,7 @@
       <c r="B24" s="56" t="s">
         <v>255</v>
       </c>
-      <c r="C24" s="89">
+      <c r="C24" s="90">
         <v>600</v>
       </c>
       <c r="D24" s="38"/>
@@ -9431,7 +9499,7 @@
       <c r="B25" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="C25" s="91"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="38"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -9440,7 +9508,7 @@
       <c r="B28" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="89">
+      <c r="C28" s="90">
         <v>900</v>
       </c>
       <c r="D28" s="38"/>
@@ -9450,7 +9518,7 @@
       <c r="B29" s="58" t="s">
         <v>261</v>
       </c>
-      <c r="C29" s="91"/>
+      <c r="C29" s="92"/>
       <c r="D29" s="38"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9458,7 +9526,7 @@
       <c r="B30" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="C30" s="89">
+      <c r="C30" s="90">
         <v>1350</v>
       </c>
       <c r="D30" s="38"/>
@@ -9468,7 +9536,7 @@
       <c r="B31" s="57" t="s">
         <v>263</v>
       </c>
-      <c r="C31" s="90"/>
+      <c r="C31" s="91"/>
       <c r="D31" s="38"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9476,7 +9544,7 @@
       <c r="B32" s="57" t="s">
         <v>264</v>
       </c>
-      <c r="C32" s="90"/>
+      <c r="C32" s="91"/>
       <c r="D32" s="38"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9484,7 +9552,7 @@
       <c r="B33" s="57" t="s">
         <v>265</v>
       </c>
-      <c r="C33" s="90"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="38"/>
     </row>
     <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9492,7 +9560,7 @@
       <c r="B34" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="C34" s="91"/>
+      <c r="C34" s="92"/>
       <c r="D34" s="38"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9500,7 +9568,7 @@
       <c r="B35" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="C35" s="89">
+      <c r="C35" s="90">
         <v>2700</v>
       </c>
       <c r="D35" s="38"/>
@@ -9510,7 +9578,7 @@
       <c r="B36" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="C36" s="90"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="38"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9518,7 +9586,7 @@
       <c r="B37" s="57" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="90"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="38"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9526,7 +9594,7 @@
       <c r="B38" s="57" t="s">
         <v>270</v>
       </c>
-      <c r="C38" s="90"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="38"/>
     </row>
     <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9534,7 +9602,7 @@
       <c r="B39" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="91"/>
+      <c r="C39" s="92"/>
       <c r="D39" s="38"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9542,7 +9610,7 @@
       <c r="B40" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="C40" s="90">
+      <c r="C40" s="91">
         <v>1500</v>
       </c>
     </row>
@@ -9551,14 +9619,14 @@
       <c r="B41" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="C41" s="91"/>
+      <c r="C41" s="92"/>
     </row>
     <row r="42" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="48"/>
       <c r="B42" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="C42" s="89">
+      <c r="C42" s="90">
         <v>2700</v>
       </c>
     </row>
@@ -9567,42 +9635,42 @@
       <c r="B43" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="C43" s="90"/>
+      <c r="C43" s="91"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="48"/>
       <c r="B44" s="57" t="s">
         <v>276</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="91"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="48"/>
       <c r="B45" s="57" t="s">
         <v>277</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="91"/>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
       <c r="B46" s="57" t="s">
         <v>279</v>
       </c>
-      <c r="C46" s="90"/>
+      <c r="C46" s="91"/>
     </row>
     <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="48"/>
       <c r="B47" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="C47" s="91"/>
+      <c r="C47" s="92"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="48"/>
       <c r="B48" s="66" t="s">
         <v>281</v>
       </c>
-      <c r="C48" s="87">
+      <c r="C48" s="88">
         <v>3000</v>
       </c>
     </row>
@@ -9611,28 +9679,28 @@
       <c r="B49" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="C49" s="92"/>
+      <c r="C49" s="93"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="48"/>
       <c r="B50" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="C50" s="92"/>
+      <c r="C50" s="93"/>
     </row>
     <row r="51" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="48"/>
       <c r="B51" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="C51" s="88"/>
+      <c r="C51" s="89"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="48"/>
       <c r="B52" s="66" t="s">
         <v>293</v>
       </c>
-      <c r="C52" s="87">
+      <c r="C52" s="88">
         <v>1500</v>
       </c>
     </row>
@@ -9641,21 +9709,21 @@
       <c r="B53" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="C53" s="92"/>
+      <c r="C53" s="93"/>
     </row>
     <row r="54" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="48"/>
       <c r="B54" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="C54" s="88"/>
+      <c r="C54" s="89"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="48"/>
       <c r="B55" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="C55" s="87">
+      <c r="C55" s="88">
         <v>1200</v>
       </c>
     </row>
@@ -9664,7 +9732,7 @@
       <c r="B56" s="58" t="s">
         <v>303</v>
       </c>
-      <c r="C56" s="88"/>
+      <c r="C56" s="89"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="48"/>
@@ -10000,7 +10068,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6078F90-1BFA-44D9-9906-5A72B5F0645C}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -10027,7 +10095,7 @@
       <c r="B2" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="89">
+      <c r="C2" s="90">
         <v>1100</v>
       </c>
       <c r="D2" s="38"/>
@@ -10037,7 +10105,7 @@
       <c r="B3" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="90"/>
+      <c r="C3" s="91"/>
       <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10045,7 +10113,7 @@
       <c r="B4" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="91"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="38"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10053,7 +10121,7 @@
       <c r="B5" s="56" t="s">
         <v>255</v>
       </c>
-      <c r="C5" s="89">
+      <c r="C5" s="90">
         <v>600</v>
       </c>
       <c r="D5" s="38"/>
@@ -10063,7 +10131,7 @@
       <c r="B6" s="58" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="91"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10081,7 +10149,7 @@
       <c r="B8" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="C8" s="89">
+      <c r="C8" s="90">
         <v>900</v>
       </c>
       <c r="D8" s="38"/>
@@ -10091,7 +10159,7 @@
       <c r="B9" s="58" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="91"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="38"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -10099,7 +10167,7 @@
       <c r="B10" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="C10" s="89">
+      <c r="C10" s="90">
         <v>1350</v>
       </c>
       <c r="D10" s="38"/>
@@ -10109,7 +10177,7 @@
       <c r="B11" s="57" t="s">
         <v>263</v>
       </c>
-      <c r="C11" s="90"/>
+      <c r="C11" s="91"/>
       <c r="D11" s="38"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10117,7 +10185,7 @@
       <c r="B12" s="57" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="90"/>
+      <c r="C12" s="91"/>
       <c r="D12" s="38"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10125,7 +10193,7 @@
       <c r="B13" s="57" t="s">
         <v>265</v>
       </c>
-      <c r="C13" s="90"/>
+      <c r="C13" s="91"/>
       <c r="D13" s="38"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10133,7 +10201,7 @@
       <c r="B14" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="C14" s="91"/>
+      <c r="C14" s="92"/>
       <c r="D14" s="38"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -10141,7 +10209,7 @@
       <c r="B15" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="C15" s="89">
+      <c r="C15" s="90">
         <v>2700</v>
       </c>
       <c r="D15" s="38"/>
@@ -10151,7 +10219,7 @@
       <c r="B16" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="C16" s="90"/>
+      <c r="C16" s="91"/>
       <c r="D16" s="38"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10159,7 +10227,7 @@
       <c r="B17" s="57" t="s">
         <v>269</v>
       </c>
-      <c r="C17" s="90"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="38"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10167,7 +10235,7 @@
       <c r="B18" s="57" t="s">
         <v>273</v>
       </c>
-      <c r="C18" s="90"/>
+      <c r="C18" s="91"/>
       <c r="D18" s="38"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10175,7 +10243,7 @@
       <c r="B19" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="91"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="38"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10183,7 +10251,7 @@
       <c r="B20" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="C20" s="90">
+      <c r="C20" s="91">
         <v>1500</v>
       </c>
       <c r="D20" s="38"/>
@@ -10193,7 +10261,7 @@
       <c r="B21" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="C21" s="91"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="38"/>
     </row>
     <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -10201,7 +10269,7 @@
       <c r="B22" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="C22" s="89">
+      <c r="C22" s="90">
         <v>2700</v>
       </c>
       <c r="D22" s="38"/>
@@ -10211,7 +10279,7 @@
       <c r="B23" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="C23" s="90"/>
+      <c r="C23" s="91"/>
       <c r="D23" s="38"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10219,7 +10287,7 @@
       <c r="B24" s="57" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="90"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="38"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10227,7 +10295,7 @@
       <c r="B25" s="57" t="s">
         <v>277</v>
       </c>
-      <c r="C25" s="90"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="38"/>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -10235,7 +10303,7 @@
       <c r="B26" s="57" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="38"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10243,7 +10311,7 @@
       <c r="B27" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="C27" s="91"/>
+      <c r="C27" s="92"/>
       <c r="D27" s="38"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10251,7 +10319,7 @@
       <c r="B28" s="66" t="s">
         <v>281</v>
       </c>
-      <c r="C28" s="87">
+      <c r="C28" s="88">
         <v>3000</v>
       </c>
       <c r="D28" s="38"/>
@@ -10261,7 +10329,7 @@
       <c r="B29" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="C29" s="92"/>
+      <c r="C29" s="93"/>
       <c r="D29" s="38"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10269,7 +10337,7 @@
       <c r="B30" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="C30" s="92"/>
+      <c r="C30" s="93"/>
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10277,7 +10345,7 @@
       <c r="B31" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="C31" s="88"/>
+      <c r="C31" s="89"/>
       <c r="D31" s="38"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10285,7 +10353,7 @@
       <c r="B32" s="66" t="s">
         <v>293</v>
       </c>
-      <c r="C32" s="87">
+      <c r="C32" s="88">
         <v>1500</v>
       </c>
       <c r="D32" s="38"/>
@@ -10295,7 +10363,7 @@
       <c r="B33" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="C33" s="92"/>
+      <c r="C33" s="93"/>
       <c r="D33" s="38"/>
     </row>
     <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10303,7 +10371,7 @@
       <c r="B34" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="C34" s="88"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="38"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10311,7 +10379,7 @@
       <c r="B35" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="C35" s="87">
+      <c r="C35" s="88">
         <v>1200</v>
       </c>
     </row>
@@ -10320,7 +10388,7 @@
       <c r="B36" s="58" t="s">
         <v>303</v>
       </c>
-      <c r="C36" s="88"/>
+      <c r="C36" s="89"/>
     </row>
     <row r="37" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="48"/>
@@ -10345,7 +10413,7 @@
       <c r="B39" s="66" t="s">
         <v>311</v>
       </c>
-      <c r="C39" s="89">
+      <c r="C39" s="90">
         <v>4800</v>
       </c>
     </row>
@@ -10354,49 +10422,49 @@
       <c r="B40" s="67" t="s">
         <v>312</v>
       </c>
-      <c r="C40" s="90"/>
+      <c r="C40" s="91"/>
     </row>
     <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="48"/>
       <c r="B41" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="C41" s="90"/>
+      <c r="C41" s="91"/>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="48"/>
       <c r="B42" s="67" t="s">
         <v>314</v>
       </c>
-      <c r="C42" s="90"/>
+      <c r="C42" s="91"/>
     </row>
     <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="48"/>
       <c r="B43" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="C43" s="90"/>
+      <c r="C43" s="91"/>
     </row>
     <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="48"/>
       <c r="B44" s="67" t="s">
         <v>315</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="91"/>
     </row>
     <row r="45" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="48"/>
       <c r="B45" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="92"/>
     </row>
     <row r="46" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
       <c r="B46" s="66" t="s">
         <v>329</v>
       </c>
-      <c r="C46" s="87">
+      <c r="C46" s="88">
         <v>7500</v>
       </c>
     </row>
@@ -10405,84 +10473,84 @@
       <c r="B47" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="92"/>
+      <c r="C47" s="93"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="48"/>
       <c r="B48" s="67" t="s">
         <v>321</v>
       </c>
-      <c r="C48" s="92"/>
+      <c r="C48" s="93"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="48"/>
       <c r="B49" s="67" t="s">
         <v>318</v>
       </c>
-      <c r="C49" s="92"/>
+      <c r="C49" s="93"/>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="48"/>
       <c r="B50" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="C50" s="92"/>
+      <c r="C50" s="93"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="48"/>
       <c r="B51" s="67" t="s">
         <v>322</v>
       </c>
-      <c r="C51" s="92"/>
+      <c r="C51" s="93"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="48"/>
       <c r="B52" s="67" t="s">
         <v>323</v>
       </c>
-      <c r="C52" s="92"/>
+      <c r="C52" s="93"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="48"/>
       <c r="B53" s="67" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="92"/>
+      <c r="C53" s="93"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="48"/>
       <c r="B54" s="67" t="s">
         <v>325</v>
       </c>
-      <c r="C54" s="92"/>
+      <c r="C54" s="93"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="48"/>
       <c r="B55" s="67" t="s">
         <v>326</v>
       </c>
-      <c r="C55" s="92"/>
+      <c r="C55" s="93"/>
     </row>
     <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="48"/>
       <c r="B56" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="C56" s="92"/>
+      <c r="C56" s="93"/>
     </row>
     <row r="57" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48"/>
       <c r="B57" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="88"/>
+      <c r="C57" s="89"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="48"/>
       <c r="B58" s="66" t="s">
         <v>330</v>
       </c>
-      <c r="C58" s="87">
+      <c r="C58" s="88">
         <v>5250</v>
       </c>
     </row>
@@ -10491,300 +10559,326 @@
       <c r="B59" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="C59" s="92"/>
+      <c r="C59" s="93"/>
     </row>
     <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="48"/>
       <c r="B60" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="C60" s="92"/>
+      <c r="C60" s="93"/>
     </row>
     <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="48"/>
       <c r="B61" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="C61" s="92"/>
+      <c r="C61" s="93"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="48"/>
       <c r="B62" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="C62" s="92"/>
+      <c r="C62" s="93"/>
     </row>
     <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="48"/>
       <c r="B63" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="C63" s="92"/>
+      <c r="C63" s="93"/>
     </row>
     <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="48"/>
       <c r="B64" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="C64" s="92"/>
+      <c r="C64" s="93"/>
     </row>
     <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="48"/>
       <c r="B65" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="C65" s="92"/>
+      <c r="C65" s="93"/>
     </row>
     <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="48"/>
       <c r="B66" s="67" t="s">
         <v>338</v>
       </c>
-      <c r="C66" s="92"/>
+      <c r="C66" s="93"/>
     </row>
     <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="48"/>
       <c r="B67" s="67" t="s">
         <v>339</v>
       </c>
-      <c r="C67" s="92"/>
+      <c r="C67" s="93"/>
     </row>
     <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="48"/>
       <c r="B68" s="67" t="s">
         <v>340</v>
       </c>
-      <c r="C68" s="92"/>
+      <c r="C68" s="93"/>
     </row>
     <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="48"/>
       <c r="B69" s="67" t="s">
         <v>341</v>
       </c>
-      <c r="C69" s="92"/>
+      <c r="C69" s="93"/>
     </row>
     <row r="70" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="48"/>
       <c r="B70" s="68" t="s">
         <v>342</v>
       </c>
-      <c r="C70" s="88"/>
-    </row>
-    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="C70" s="89"/>
+    </row>
+    <row r="71" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="48"/>
-      <c r="B71" s="62" t="s">
+      <c r="B71" s="72" t="s">
         <v>355</v>
       </c>
-      <c r="C71" s="63">
+      <c r="C71" s="69">
         <v>3000</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="48"/>
-      <c r="B72" s="62"/>
-      <c r="C72" s="63"/>
-    </row>
-    <row r="73" spans="1:3" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="51"/>
-      <c r="B73" s="52"/>
-      <c r="C73" s="53"/>
+      <c r="B72" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="C72" s="69">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="48"/>
+      <c r="B73" s="62"/>
+      <c r="C73" s="63"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="43"/>
-      <c r="B74" s="43" t="s">
+      <c r="A74" s="48"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="63"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="48"/>
+      <c r="B75" s="62"/>
+      <c r="C75" s="63"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="48"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="63"/>
+    </row>
+    <row r="77" spans="1:3" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="51"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="53"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="43"/>
+      <c r="B78" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="C74" s="46">
-        <f>SUM(C2:C73)</f>
-        <v>41150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
+      <c r="C78" s="46">
+        <f>SUM(C2:C77)</f>
+        <v>41750</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="55">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="55">
         <v>45690</v>
       </c>
-      <c r="B76" s="48" t="s">
+      <c r="B80" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C76" s="54">
+      <c r="C80" s="54">
         <v>2300</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="55"/>
-      <c r="B77" s="48" t="s">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="55"/>
+      <c r="B81" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="54">
+      <c r="C81" s="54">
         <v>2250</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="55">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="55">
         <v>45804</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B82" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="C78" s="54">
+      <c r="C82" s="54">
         <v>2700</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="55">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="55">
         <v>45839</v>
       </c>
-      <c r="B79" s="48" t="s">
+      <c r="B83" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="C79" s="54">
+      <c r="C83" s="54">
         <v>4200</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="55"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="54">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="55"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="54">
         <v>4500</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="55">
-        <v>46266</v>
-      </c>
-      <c r="B81" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="C81" s="54">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="55"/>
-      <c r="B82" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="C82" s="54">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="55">
-        <v>46073</v>
-      </c>
-      <c r="B83" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="C83" s="54">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="55">
-        <v>46089</v>
-      </c>
-      <c r="B84" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="C84" s="54">
-        <v>6000</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="55">
+        <v>46266</v>
+      </c>
+      <c r="B85" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C85" s="54">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="55"/>
+      <c r="B86" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C86" s="54">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="55">
+        <v>46073</v>
+      </c>
+      <c r="B87" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C87" s="54">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="55">
+        <v>46089</v>
+      </c>
+      <c r="B88" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C88" s="54">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="55">
         <v>46105</v>
       </c>
-      <c r="B85" s="48"/>
-      <c r="C85" s="54">
+      <c r="B89" s="48"/>
+      <c r="C89" s="54">
         <v>5000</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="55">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="55">
         <v>46141</v>
       </c>
-      <c r="B86" s="48"/>
-      <c r="C86" s="54">
+      <c r="B90" s="48"/>
+      <c r="C90" s="54">
         <v>1500</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="55"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="54"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="55"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="54"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="55"/>
-      <c r="B89" s="48"/>
-      <c r="C89" s="54"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="48"/>
-      <c r="B90" s="48"/>
-      <c r="C90" s="54"/>
-    </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="43"/>
-      <c r="B91" s="43" t="s">
+      <c r="A91" s="55"/>
+      <c r="B91" s="48"/>
+      <c r="C91" s="54">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="55"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="54"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="55"/>
+      <c r="B93" s="48"/>
+      <c r="C93" s="54"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="48"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="54"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="43"/>
+      <c r="B95" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="C91" s="46">
-        <f>SUM(C75:C90)</f>
-        <v>37900</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6" t="s">
+      <c r="C95" s="46">
+        <f>SUM(C79:C94)</f>
+        <v>41150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C92" s="47">
-        <f>C74-C91</f>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B96" s="13" t="s">
+      <c r="C96" s="47">
+        <f>C78-C95</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B100" s="13" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" s="13" t="s">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="13" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="98" spans="2:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B98" s="13" t="s">
+    <row r="102" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B102" s="13" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="99" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B99" s="13" t="s">
+    <row r="103" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B103" s="13" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="100" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B100" s="13" t="s">
+    <row r="104" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B104" s="13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="101" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B101" s="13" t="s">
+    <row r="105" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B105" s="13" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B102" s="13" t="s">
+    <row r="106" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B106" s="13" t="s">
         <v>317</v>
       </c>
     </row>
